--- a/data/trans_dic/IP09B02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,73; 76,41</t>
+          <t>25,72; 75,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,64; 60,57</t>
+          <t>26,18; 61,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 45,1</t>
+          <t>5,48; 45,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,38; 82,83</t>
+          <t>25,34; 82,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,93; 95,33</t>
+          <t>58,35; 95,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,78; 57,56</t>
+          <t>23,57; 58,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,36; 65,09</t>
+          <t>22,74; 66,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,92; 73,92</t>
+          <t>26,06; 71,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51,75; 83,0</t>
+          <t>53,74; 83,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,67; 53,81</t>
+          <t>28,98; 53,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,83; 51,02</t>
+          <t>18,45; 50,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,57; 70,31</t>
+          <t>34,55; 68,99</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,73; 87,72</t>
+          <t>60,38; 88,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,3; 83,35</t>
+          <t>58,91; 84,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,01; 78,13</t>
+          <t>42,9; 79,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,33; 95,4</t>
+          <t>48,69; 95,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,3; 85,25</t>
+          <t>62,43; 85,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,0; 80,12</t>
+          <t>55,77; 81,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,07; 70,18</t>
+          <t>35,65; 71,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,74; 80,53</t>
+          <t>51,59; 82,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,13; 83,22</t>
+          <t>66,47; 84,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61,65; 79,6</t>
+          <t>60,9; 79,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,09; 69,68</t>
+          <t>44,02; 71,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,81; 82,84</t>
+          <t>54,77; 82,3</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,36; 90,57</t>
+          <t>49,71; 90,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,47; 80,17</t>
+          <t>44,68; 82,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,25; 91,94</t>
+          <t>35,65; 89,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,94; 95,47</t>
+          <t>64,19; 95,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70,41; 100,0</t>
+          <t>66,18; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,66; 78,22</t>
+          <t>37,09; 78,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,21; 87,57</t>
+          <t>22,96; 87,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59,74; 89,92</t>
+          <t>56,83; 89,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,45; 92,06</t>
+          <t>69,01; 92,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49,13; 75,11</t>
+          <t>47,59; 75,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,25; 82,04</t>
+          <t>39,65; 83,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,19; 89,89</t>
+          <t>67,29; 89,87</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,73; 92,02</t>
+          <t>42,87; 92,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,03; 84,24</t>
+          <t>41,9; 85,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,19; 70,19</t>
+          <t>22,62; 72,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70,18; 95,45</t>
+          <t>70,77; 95,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,3; 96,39</t>
+          <t>72,98; 96,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,51; 90,25</t>
+          <t>59,88; 89,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,14; 88,49</t>
+          <t>40,24; 87,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68,57; 94,31</t>
+          <t>68,4; 94,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,66; 94,33</t>
+          <t>70,2; 92,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,58; 83,36</t>
+          <t>58,66; 84,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40,34; 75,01</t>
+          <t>38,68; 74,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,95; 91,68</t>
+          <t>74,22; 91,95</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,04; 79,53</t>
+          <t>60,4; 80,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,97; 70,41</t>
+          <t>53,45; 71,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,66; 62,55</t>
+          <t>39,46; 64,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70,22; 88,39</t>
+          <t>70,86; 89,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>74,61; 87,96</t>
+          <t>75,03; 88,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,32; 70,98</t>
+          <t>54,88; 71,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,35; 66,85</t>
+          <t>42,5; 65,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>66,16; 83,51</t>
+          <t>64,66; 82,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,76; 83,16</t>
+          <t>71,64; 83,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56,39; 68,05</t>
+          <t>56,71; 68,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45,34; 61,22</t>
+          <t>44,71; 61,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,55; 83,15</t>
+          <t>69,98; 82,88</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4600</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8783</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2111</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4674</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11575</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8775</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5346</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5683</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16174</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17558</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7457</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>10357</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2401; 7055</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5336; 12489</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>531; 4435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2071; 6764</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8276; 13529</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5205; 12820</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2873; 8361</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2984; 8233</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12639; 19534</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>12306; 22811</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4116; 11227</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>6778; 13536</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>18642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20629</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11731</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7410</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26487</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26303</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11255</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>15386</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>45130</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>46932</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>22985</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>22795</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>14893; 21854</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16664; 23968</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7943; 14658</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4524; 8879</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>21937; 29927</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>21077; 30787</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7510; 15085</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>11689; 18605</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>39752; 50344</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>40242; 52585</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>17427; 28196</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>17500; 26294</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10322</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13097</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5627</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14303</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13521</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8803</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3615</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>18024</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>23843</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>21900</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9242</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>32326</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>6809; 12404</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9024; 16579</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2987; 7524</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10744; 15959</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9952; 15038</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5549; 11732</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1362; 5189</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>13314; 20865</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>19831; 26617</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16732; 26438</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5674; 12006</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>27027; 36097</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5832</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8766</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4723</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25155</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15748</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18126</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8214</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>34355</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>21580</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>26891</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12936</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>59510</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3376; 7265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5604; 11409</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2386; 7647</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>20769; 28026</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>12968; 17121</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>14043; 21032</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4755; 10393</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>28381; 39107</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>18002; 23719</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>21601; 31036</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>8648; 16575</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>52578; 65136</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>39396</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>51274</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>24192</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>51540</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>67331</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>62007</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28429</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>73448</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>106727</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>113281</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>52621</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>124989</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>33568; 44653</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>43961; 58425</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18596; 30253</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>45028; 56624</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>61625; 72284</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>53943; 70547</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>21865; 33701</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>64030; 82179</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>98650; 114986</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>102383; 123457</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>44075; 60958</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>113774; 134739</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09B02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,72; 75,56</t>
+          <t>21,45; 75,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,18; 61,28</t>
+          <t>25,15; 62,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 45,8</t>
+          <t>5,47; 45,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,34; 82,76</t>
+          <t>29,9; 83,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,35; 95,39</t>
+          <t>62,0; 95,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,57; 58,07</t>
+          <t>24,5; 58,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,74; 66,2</t>
+          <t>20,12; 64,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,06; 71,91</t>
+          <t>27,42; 72,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,74; 83,06</t>
+          <t>52,09; 82,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,98; 53,72</t>
+          <t>29,7; 54,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,45; 50,31</t>
+          <t>20,43; 51,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,55; 68,99</t>
+          <t>35,45; 69,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>60,38; 88,6</t>
+          <t>58,01; 87,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,91; 84,73</t>
+          <t>56,3; 83,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,9; 79,16</t>
+          <t>45,35; 78,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,69; 95,56</t>
+          <t>48,49; 95,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,43; 85,16</t>
+          <t>62,66; 85,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,77; 81,46</t>
+          <t>56,92; 80,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,65; 71,6</t>
+          <t>34,86; 71,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,59; 82,11</t>
+          <t>50,4; 81,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,47; 84,18</t>
+          <t>65,43; 83,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60,9; 79,58</t>
+          <t>62,04; 79,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,02; 71,23</t>
+          <t>45,04; 69,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,77; 82,3</t>
+          <t>58,16; 83,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,71; 90,54</t>
+          <t>53,6; 91,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,68; 82,08</t>
+          <t>45,45; 80,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,65; 89,79</t>
+          <t>37,36; 92,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64,19; 95,35</t>
+          <t>61,53; 95,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,18; 100,0</t>
+          <t>66,43; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,09; 78,42</t>
+          <t>38,18; 78,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,96; 87,49</t>
+          <t>23,16; 87,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56,83; 89,06</t>
+          <t>57,1; 90,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69,01; 92,62</t>
+          <t>68,28; 92,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,59; 75,19</t>
+          <t>48,49; 75,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,65; 83,9</t>
+          <t>41,56; 84,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,29; 89,87</t>
+          <t>67,93; 90,34</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,87; 92,27</t>
+          <t>45,95; 92,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,9; 85,3</t>
+          <t>43,93; 84,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,62; 72,52</t>
+          <t>16,37; 71,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70,77; 95,5</t>
+          <t>70,12; 95,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,98; 96,35</t>
+          <t>72,99; 96,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,88; 89,68</t>
+          <t>59,25; 89,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,24; 87,96</t>
+          <t>42,9; 88,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68,4; 94,25</t>
+          <t>67,53; 94,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,2; 92,5</t>
+          <t>68,97; 92,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,66; 84,28</t>
+          <t>58,96; 83,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38,68; 74,12</t>
+          <t>40,17; 74,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,22; 91,95</t>
+          <t>74,67; 92,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>60,4; 80,35</t>
+          <t>60,24; 79,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53,45; 71,04</t>
+          <t>54,06; 70,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,46; 64,2</t>
+          <t>39,33; 62,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70,86; 89,1</t>
+          <t>71,89; 89,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>75,03; 88,01</t>
+          <t>74,32; 88,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,88; 71,78</t>
+          <t>55,36; 70,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,5; 65,51</t>
+          <t>44,22; 66,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,66; 82,99</t>
+          <t>64,55; 83,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,64; 83,5</t>
+          <t>71,47; 82,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56,71; 68,39</t>
+          <t>56,51; 67,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44,71; 61,84</t>
+          <t>46,0; 61,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>69,98; 82,88</t>
+          <t>70,47; 83,51</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2401; 7055</t>
+          <t>2002; 7041</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5336; 12489</t>
+          <t>5125; 12673</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>531; 4435</t>
+          <t>530; 4422</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2071; 6764</t>
+          <t>2444; 6856</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8276; 13529</t>
+          <t>8793; 13540</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5205; 12820</t>
+          <t>5408; 13003</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2873; 8361</t>
+          <t>2542; 8132</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2984; 8233</t>
+          <t>3139; 8339</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12639; 19534</t>
+          <t>12252; 19513</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12306; 22811</t>
+          <t>12609; 23044</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4116; 11227</t>
+          <t>4558; 11484</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6778; 13536</t>
+          <t>6956; 13711</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14893; 21854</t>
+          <t>14309; 21694</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16664; 23968</t>
+          <t>15925; 23753</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7943; 14658</t>
+          <t>8398; 14566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4524; 8879</t>
+          <t>4506; 8877</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21937; 29927</t>
+          <t>22018; 29979</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21077; 30787</t>
+          <t>21513; 30427</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7510; 15085</t>
+          <t>7346; 15131</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11689; 18605</t>
+          <t>11421; 18533</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39752; 50344</t>
+          <t>39129; 50027</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40242; 52585</t>
+          <t>40994; 52751</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17427; 28196</t>
+          <t>17828; 27598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17500; 26294</t>
+          <t>18581; 26551</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6809; 12404</t>
+          <t>7343; 12511</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9024; 16579</t>
+          <t>9181; 16208</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2987; 7524</t>
+          <t>3131; 7773</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10744; 15959</t>
+          <t>10299; 15944</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9952; 15038</t>
+          <t>9990; 15038</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5549; 11732</t>
+          <t>5712; 11803</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1362; 5189</t>
+          <t>1374; 5204</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13314; 20865</t>
+          <t>13377; 21113</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19831; 26617</t>
+          <t>19621; 26619</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16732; 26438</t>
+          <t>17050; 26680</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5674; 12006</t>
+          <t>5947; 12027</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27027; 36097</t>
+          <t>27284; 36287</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3376; 7265</t>
+          <t>3618; 7258</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5604; 11409</t>
+          <t>5876; 11352</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2386; 7647</t>
+          <t>1726; 7585</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20769; 28026</t>
+          <t>20577; 28072</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12968; 17121</t>
+          <t>12970; 17117</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14043; 21032</t>
+          <t>13895; 21028</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4755; 10393</t>
+          <t>5069; 10411</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28381; 39107</t>
+          <t>28018; 39052</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18002; 23719</t>
+          <t>17685; 23718</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21601; 31036</t>
+          <t>21712; 30871</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8648; 16575</t>
+          <t>8983; 16700</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>52578; 65136</t>
+          <t>52892; 65726</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33568; 44653</t>
+          <t>33479; 44264</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43961; 58425</t>
+          <t>44459; 58200</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18596; 30253</t>
+          <t>18533; 29516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45028; 56624</t>
+          <t>45687; 56596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>61625; 72284</t>
+          <t>61042; 72400</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53943; 70547</t>
+          <t>54405; 69358</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21865; 33701</t>
+          <t>22748; 34242</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>64030; 82179</t>
+          <t>63923; 82207</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>98650; 114986</t>
+          <t>98413; 114016</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>102383; 123457</t>
+          <t>102009; 122446</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44075; 60958</t>
+          <t>45337; 61043</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>113774; 134739</t>
+          <t>114571; 135763</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09B02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>81,61%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39,74%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42,33%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>50,22%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>49,27%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>43,1%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>21,8%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>57,19%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>81,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,74%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,33%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,43%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,45; 75,42</t>
+          <t>57,93; 95,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,15; 62,18</t>
+          <t>22,78; 57,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 45,68</t>
+          <t>20,36; 65,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,9; 83,89</t>
+          <t>27,51; 74,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,0; 95,47</t>
+          <t>23,73; 76,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,5; 58,89</t>
+          <t>26,64; 60,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,12; 64,38</t>
+          <t>5,23; 45,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,42; 72,84</t>
+          <t>24,59; 82,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,09; 82,97</t>
+          <t>51,75; 83,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,7; 54,27</t>
+          <t>28,67; 53,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,43; 51,47</t>
+          <t>20,83; 51,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,45; 69,87</t>
+          <t>33,99; 70,17</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75,37%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>69,6%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53,42%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68,99%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>75,58%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>72,92%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>63,36%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>79,74%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>75,37%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>69,6%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>53,42%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>72,41%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,01; 87,95</t>
+          <t>60,3; 85,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,3; 83,97</t>
+          <t>56,0; 80,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,35; 78,67</t>
+          <t>34,07; 70,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,49; 95,53</t>
+          <t>50,8; 81,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,66; 85,31</t>
+          <t>58,73; 87,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,92; 80,51</t>
+          <t>57,3; 83,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,86; 71,82</t>
+          <t>45,01; 78,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,4; 81,79</t>
+          <t>48,09; 95,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,43; 83,65</t>
+          <t>64,13; 83,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62,04; 79,83</t>
+          <t>61,65; 79,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,04; 69,72</t>
+          <t>45,09; 69,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,16; 83,1</t>
+          <t>59,29; 83,41</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>58,84%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60,95%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76,36%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>75,35%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>64,84%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>67,16%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>85,45%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>89,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>60,95%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,6; 91,32</t>
+          <t>70,41; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,45; 80,24</t>
+          <t>37,66; 78,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,36; 92,77</t>
+          <t>24,21; 87,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,53; 95,25</t>
+          <t>58,52; 89,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,43; 100,0</t>
+          <t>52,36; 90,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,18; 78,89</t>
+          <t>46,47; 80,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,16; 87,74</t>
+          <t>34,25; 91,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57,1; 90,12</t>
+          <t>61,12; 95,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68,28; 92,63</t>
+          <t>70,45; 92,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,49; 75,88</t>
+          <t>49,13; 75,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,56; 84,05</t>
+          <t>37,25; 82,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,93; 90,34</t>
+          <t>66,96; 89,61</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>88,62%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>77,29%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69,51%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>80,65%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>74,07%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>65,54%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>44,79%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>85,72%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>88,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>77,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,51%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>81,49%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,95; 92,18</t>
+          <t>73,3; 96,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,93; 84,87</t>
+          <t>61,51; 90,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,37; 71,93</t>
+          <t>46,14; 88,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70,12; 95,66</t>
+          <t>65,2; 92,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,99; 96,33</t>
+          <t>40,73; 92,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,25; 89,67</t>
+          <t>40,03; 84,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,9; 88,11</t>
+          <t>21,19; 70,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67,53; 94,12</t>
+          <t>67,59; 93,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68,97; 92,49</t>
+          <t>69,66; 94,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,96; 83,83</t>
+          <t>59,58; 83,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40,17; 74,68</t>
+          <t>40,34; 75,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,67; 92,78</t>
+          <t>71,18; 89,65</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>63,09%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73,91%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>70,89%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>62,34%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>51,34%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>81,1%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>81,98%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>63,09%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>55,26%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>60,24; 79,65</t>
+          <t>74,61; 87,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,06; 70,77</t>
+          <t>55,32; 70,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,33; 62,64</t>
+          <t>43,35; 66,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71,89; 89,06</t>
+          <t>65,36; 82,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>74,32; 88,15</t>
+          <t>59,04; 79,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,36; 70,57</t>
+          <t>52,97; 70,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,22; 66,56</t>
+          <t>39,66; 62,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,55; 83,01</t>
+          <t>69,21; 86,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,47; 82,8</t>
+          <t>71,76; 83,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56,51; 67,83</t>
+          <t>56,39; 68,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,0; 61,93</t>
+          <t>45,34; 61,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,47; 83,51</t>
+          <t>69,61; 82,22</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11575</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8775</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5346</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4722</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4600</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>8783</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2111</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4674</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>11575</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8775</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5346</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>9012</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2002; 7041</t>
+          <t>8216; 13521</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5125; 12673</t>
+          <t>5029; 12710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>530; 4422</t>
+          <t>2572; 8221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2444; 6856</t>
+          <t>2586; 6998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8793; 13540</t>
+          <t>2215; 7133</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5408; 13003</t>
+          <t>5429; 12344</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2542; 8132</t>
+          <t>507; 4367</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3139; 8339</t>
+          <t>1915; 6418</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12252; 19513</t>
+          <t>12172; 19521</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12609; 23044</t>
+          <t>12172; 22848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4558; 11484</t>
+          <t>4648; 11385</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6956; 13711</t>
+          <t>5843; 12061</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26487</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26303</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11255</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13040</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>18642</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>20629</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11731</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7410</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26487</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>26303</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11255</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22795</t>
+          <t>20123</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14309; 21694</t>
+          <t>21188; 29956</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15925; 23753</t>
+          <t>21164; 30279</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8398; 14566</t>
+          <t>7179; 14785</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4506; 8877</t>
+          <t>9602; 15481</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22018; 29979</t>
+          <t>14486; 21637</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21513; 30427</t>
+          <t>16208; 23578</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7346; 15131</t>
+          <t>8335; 14467</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11421; 18533</t>
+          <t>4275; 8518</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39129; 50027</t>
+          <t>38352; 49770</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40994; 52751</t>
+          <t>40736; 52602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17828; 27598</t>
+          <t>17850; 27581</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18581; 26551</t>
+          <t>16478; 23182</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13521</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8803</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3615</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16456</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>10322</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>13097</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5627</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14303</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13521</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8803</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3615</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32326</t>
+          <t>30951</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7343; 12511</t>
+          <t>10588; 15038</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9181; 16208</t>
+          <t>5634; 11702</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3131; 7773</t>
+          <t>1436; 5194</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10299; 15944</t>
+          <t>12611; 19300</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9990; 15038</t>
+          <t>7172; 12407</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5712; 11803</t>
+          <t>9387; 16194</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1374; 5204</t>
+          <t>2870; 7704</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13377; 21113</t>
+          <t>10432; 16288</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19621; 26619</t>
+          <t>20245; 26457</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17050; 26680</t>
+          <t>17273; 26409</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5947; 12027</t>
+          <t>5331; 11740</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27284; 36287</t>
+          <t>25861; 34607</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15748</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18126</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8214</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31465</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5832</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8766</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4723</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25155</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15748</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>18126</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8214</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34355</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59510</t>
+          <t>52439</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3618; 7258</t>
+          <t>13025; 17127</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5876; 11352</t>
+          <t>14425; 21165</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1726; 7585</t>
+          <t>5451; 10456</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20577; 28072</t>
+          <t>25440; 36144</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12970; 17117</t>
+          <t>3207; 7245</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13895; 21028</t>
+          <t>5354; 11267</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5069; 10411</t>
+          <t>2235; 7402</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28018; 39052</t>
+          <t>17126; 23666</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17685; 23718</t>
+          <t>17862; 24188</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21712; 30871</t>
+          <t>21939; 30697</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8983; 16700</t>
+          <t>9020; 16773</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>52892; 65726</t>
+          <t>45804; 57692</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67331</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>62007</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28429</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>65683</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>39396</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>51274</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>24192</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>51540</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>67331</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>62007</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>28429</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73448</t>
+          <t>46842</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>124989</t>
+          <t>112525</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33479; 44264</t>
+          <t>61277; 72241</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44459; 58200</t>
+          <t>54369; 69759</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18533; 29516</t>
+          <t>22300; 34394</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45687; 56596</t>
+          <t>58089; 73728</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>61042; 72400</t>
+          <t>32809; 44199</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54405; 69358</t>
+          <t>43562; 57908</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22748; 34242</t>
+          <t>18689; 29474</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>63923; 82207</t>
+          <t>40889; 51248</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>98413; 114016</t>
+          <t>98818; 114513</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>102009; 122446</t>
+          <t>101791; 122853</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45337; 61043</t>
+          <t>44687; 60342</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>114571; 135763</t>
+          <t>102983; 121641</t>
         </is>
       </c>
     </row>
